--- a/atividades.xlsx
+++ b/atividades.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\francisco.silva\Desktop\Dev\TopogfRegisto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\francisco.silva\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A111F34-A7E7-42F0-82D5-9336807306BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83D5157B-9C66-42CD-8DD9-9CD5D23E2DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30270" yWindow="1470" windowWidth="28800" windowHeight="15345" xr2:uid="{26643F2A-5166-4B3D-8E38-EBFFACE0483A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{26643F2A-5166-4B3D-8E38-EBFFACE0483A}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -76,8 +76,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -162,20 +170,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,62 +538,62 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="4"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="6"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="4"/>
     </row>
     <row r="4" spans="2:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="6" t="s">
         <v>7</v>
       </c>
     </row>

--- a/atividades.xlsx
+++ b/atividades.xlsx
@@ -1,25 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\francisco.silva\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83D5157B-9C66-42CD-8DD9-9CD5D23E2DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EB539C1-FB3A-43A3-B15F-C84903120D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{26643F2A-5166-4B3D-8E38-EBFFACE0483A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,47 +28,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+  <si>
+    <t>Tabela 1</t>
+  </si>
+  <si>
+    <t>Tabela 2</t>
+  </si>
   <si>
     <t>Técnico</t>
   </si>
   <si>
+    <t>Data Início</t>
+  </si>
+  <si>
+    <t>Data Fim</t>
+  </si>
+  <si>
+    <t>Horas</t>
+  </si>
+  <si>
     <t>Local/Obra</t>
   </si>
   <si>
+    <t>Nº Obra</t>
+  </si>
+  <si>
     <t>Serviço</t>
   </si>
   <si>
     <t>Anexo</t>
-  </si>
-  <si>
-    <t>Horas</t>
-  </si>
-  <si>
-    <t>Tabela 1</t>
-  </si>
-  <si>
-    <t>Tabela 2</t>
   </si>
   <si>
     <t>Total 
 Horas</t>
   </si>
   <si>
-    <t>Data Início</t>
-  </si>
-  <si>
-    <t>Data Fim</t>
-  </si>
-  <si>
-    <t>Nº Obra</t>
+    <t>Tabela 3</t>
+  </si>
+  <si>
+    <t>Total
+Horas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,7 +92,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -101,7 +114,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -113,21 +126,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -161,28 +159,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -518,14 +558,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF7CD4B-78B1-48B4-9F42-9182FAAE2BC1}">
-  <dimension ref="B3:O4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B3:R4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.42578125" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" customWidth="1"/>
     <col min="6" max="6" width="27.42578125" customWidth="1"/>
     <col min="7" max="7" width="10.5703125" customWidth="1"/>
     <col min="8" max="8" width="33.7109375" customWidth="1"/>
@@ -535,72 +575,87 @@
     <col min="14" max="14" width="9.140625" customWidth="1"/>
     <col min="15" max="15" width="8.28515625" customWidth="1"/>
     <col min="16" max="16" width="12.42578125" customWidth="1"/>
+    <col min="17" max="17" width="12.85546875" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
+    <row r="3" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="6"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="R3" s="8"/>
+    </row>
+    <row r="4" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-    </row>
-    <row r="4" spans="2:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="I4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>3</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="5" t="s">
+      <c r="L4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="6" t="s">
-        <v>7</v>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="L3:O3"/>
+    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/atividades.xlsx
+++ b/atividades.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EB539C1-FB3A-43A3-B15F-C84903120D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" codeName="EsteLivro" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C2D43F-E584-4713-B27D-FF6B362997D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -204,6 +204,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -218,12 +224,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,7 +559,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:R4"/>
+  <sheetPr codeName="Folha1"/>
+  <dimension ref="B3:R6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.42578125" customWidth="1"/>
@@ -580,29 +581,29 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="8"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="7" t="s">
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="8"/>
+      <c r="R3" s="10"/>
     </row>
     <row r="4" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -643,12 +644,24 @@
       <c r="O4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P4" s="9"/>
+      <c r="P4" s="4"/>
       <c r="Q4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="10" t="s">
+      <c r="R4" s="5" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="R5">
+        <f>SUMIF(L$5:L$100, Q5, O$5:O$100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="R6">
+        <f>SUMIF(L$5:L$100, Q6, O$5:O$100)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/atividades.xlsx
+++ b/atividades.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" codeName="EsteLivro" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C2D43F-E584-4713-B27D-FF6B362997D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2242C11A-F0BC-4557-AAD2-436B00C671EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Tabela 1</t>
   </si>
@@ -69,6 +69,12 @@
   <si>
     <t>Total
 Horas</t>
+  </si>
+  <si>
+    <t>Daniel P</t>
+  </si>
+  <si>
+    <t>Francisco S</t>
   </si>
 </sst>
 </file>
@@ -653,12 +659,18 @@
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q5" t="s">
+        <v>13</v>
+      </c>
       <c r="R5">
         <f>SUMIF(L$5:L$100, Q5, O$5:O$100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q6" t="s">
+        <v>14</v>
+      </c>
       <c r="R6">
         <f>SUMIF(L$5:L$100, Q6, O$5:O$100)</f>
         <v>0</v>

--- a/atividades.xlsx
+++ b/atividades.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" codeName="EsteLivro" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2242C11A-F0BC-4557-AAD2-436B00C671EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC5E5F2-8228-44DD-BE9F-2004EA98661A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -231,6 +231,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -659,19 +660,19 @@
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="Q5" t="s">
+      <c r="Q5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="11">
         <f>SUMIF(L$5:L$100, Q5, O$5:O$100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="Q6" t="s">
+      <c r="Q6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="11">
         <f>SUMIF(L$5:L$100, Q6, O$5:O$100)</f>
         <v>0</v>
       </c>
